--- a/nonprofit_employee_forms/018_human_rights_petition_form--nonprofit_employee_forms.xlsx
+++ b/nonprofit_employee_forms/018_human_rights_petition_form--nonprofit_employee_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select One 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select Multiple 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>select_one_date</t>
+          <t>select_one_date_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Select One Date</t>
+          <t>Select One Date 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>select_multiple_date</t>
+          <t>select_multiple_date_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Select Multiple Date</t>
+          <t>Select Multiple Date 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>select_one_time</t>
+          <t>select_one_time_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Select One Time</t>
+          <t>Select One Time 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>select_multiple_time</t>
+          <t>select_multiple_time_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Select Multiple Time</t>
+          <t>Select Multiple Time 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one_date_choices</t>
+          <t>select_one_date_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one_date_choices</t>
+          <t>select_one_date_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple_date_choices</t>
+          <t>select_multiple_date_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple_date_choices</t>
+          <t>select_multiple_date_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_one_time_choices</t>
+          <t>select_one_time_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_one_time_choices</t>
+          <t>select_one_time_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_multiple_time_choices</t>
+          <t>select_multiple_time_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>select_multiple_time_choices</t>
+          <t>select_multiple_time_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
